--- a/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
@@ -175,13 +175,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -194,9 +197,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -351,12 +351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'NAV Trend'!$A$4:$A$149</f>
+              <f>'NAV Trend'!$A$4:$A$150</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'NAV Trend'!$B$4:$B$149</f>
+              <f>'NAV Trend'!$B$4:$B$150</f>
             </numRef>
           </val>
         </ser>
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-02  ·  Generated 2026-06-04T18:48:22  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-03  ·  Generated 2026-06-10T09:47:13  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3.365</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.988</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2.391</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46952.31</v>
+        <v>38394.23</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>41.05</v>
+        <v>33.43</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.775</v>
+        <v>1.889</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.9504</v>
+        <v>0.9591</v>
       </c>
     </row>
     <row r="13">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>8.09 / 4.04</t>
+          <t>9.08 / 4.54</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3.365</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>MS (34.24% NAV)</t>
+          <t>BWA (32.58% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>24.78</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="18">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>46952.31</v>
+        <v>38394.23</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>66389.7</v>
+        <v>54288.74</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>453097.11</v>
+        <v>370510.33</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>41.05</v>
+        <v>33.43</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37348.13</v>
+        <v>26685.64</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41473.89</v>
+        <v>28974.03</v>
       </c>
     </row>
     <row r="10">
@@ -1024,131 +1024,131 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9569.200000000001</v>
+        <v>5927.26</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>20.38</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>5953.12</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>12.68</v>
+        <v>4816.52</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>12.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4733.32</v>
+        <v>3890.43</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10.08</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>3788.65</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>8.07</v>
+        <v>3182.2</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>3114.3</v>
+        <v>2784.76</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6.63</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2699.74</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>5.75</v>
+        <v>2127.92</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2047.87</v>
+        <v>2056.89</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>4.36</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1974.98</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>4.21</v>
+        <v>2008.59</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1885.69</v>
+        <v>1774.32</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4.02</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1839.9</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>3.92</v>
+        <v>1703.79</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>4.44</v>
       </c>
     </row>
     <row r="22">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1834.25</v>
+        <v>1687.93</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="23">
@@ -1171,49 +1171,49 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1577.63</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>3.36</v>
+        <v>1647.3</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>4.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1577.37</v>
+        <v>1455.49</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3.36</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1559.37</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>3.32</v>
+        <v>1348.72</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>3.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1142.7</v>
+        <v>808.65</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -1284,61 +1284,61 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2676</v>
+        <v>312</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1833129</v>
+        <v>1641677</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+          <t>MTD</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
-        <v>312</v>
+      <c r="C7" s="15" t="n">
+        <v>82</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1691876</v>
-      </c>
-      <c r="E7" s="16" t="n">
+        <v>221093</v>
+      </c>
+      <c r="E7" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
-        <v>82</v>
+          <t>ODFL/MKTX</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>262</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>217027</v>
+        <v>1848126</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1347,21 +1347,21 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>MS/AWK</t>
+          <t>MKTX</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1758</v>
+        <v>396</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>5467313</v>
-      </c>
-      <c r="E9" s="16" t="n">
+        <v>655942</v>
+      </c>
+      <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,14 +1373,14 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1882952</v>
+        <v>1848126</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1389,40 +1389,40 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>MKTX</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/MKTX</t>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>396</v>
+        <v>191</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>645029</v>
-      </c>
-      <c r="E11" s="16" t="n">
+        <v>1445656</v>
+      </c>
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>128</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>67</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1882952</v>
+        <v>1015148</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1431,40 +1431,40 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/JKHY</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>191</v>
+          <t>REGN</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>23</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1422335</v>
-      </c>
-      <c r="E13" s="16" t="n">
+        <v>1013604</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>67</v>
+          <t>PANW/IQV</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>233</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1023854</v>
+        <v>10177295</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1473,40 +1473,40 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>REGN</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="n">
-        <v>23</v>
+          <t>IQV</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>PANW/IQV</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>350</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1019102</v>
-      </c>
-      <c r="E15" s="16" t="n">
+        <v>1843070</v>
+      </c>
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>PANW/IQV</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>233</v>
+          <t>KLAC/LOW</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>42</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>9698986</v>
+        <v>1015148</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1515,40 +1515,40 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>IQV</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>PANW/IQV</t>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1890942</v>
-      </c>
-      <c r="E17" s="16" t="n">
+        <v>3117460</v>
+      </c>
+      <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>42</v>
+          <t>FFIV/VLTO</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>426</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1023854</v>
+        <v>751751</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1557,40 +1557,40 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/LOW</t>
+          <t>VLTO</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>382</v>
+        <v>665</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>3061039</v>
-      </c>
-      <c r="E19" s="16" t="n">
+        <v>2459103</v>
+      </c>
+      <c r="E19" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>748678</v>
+        <v>9020600</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1648,11 +1648,11 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>-131966.85</v>
-      </c>
-      <c r="C4" s="21" t="n">
-        <v>-11.96</v>
+      <c r="B4" s="19" t="n">
+        <v>-101586.44</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>-9.17</v>
       </c>
     </row>
     <row r="5">
@@ -1661,11 +1661,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>-263933.69</v>
+      <c r="B5" s="18" t="n">
+        <v>-203172.89</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-23.91</v>
+        <v>-18.33</v>
       </c>
     </row>
     <row r="6">
@@ -1674,11 +1674,11 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>-131966.85</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>-11.96</v>
+      <c r="B6" s="19" t="n">
+        <v>-101586.44</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>-9.17</v>
       </c>
     </row>
     <row r="7">
@@ -1687,11 +1687,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
-        <v>-92044.88</v>
+      <c r="B7" s="18" t="n">
+        <v>-92663.67999999999</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-8.34</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>3</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>6.29</v>
+        <v>5.38</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>34.24</v>
+        <v>32.58</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>31.66</v>
+        <v>26.73</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1915,54 +1915,54 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>AWK</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="D10" s="32" t="n">
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="D10" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
-        <v>24.78</v>
-      </c>
-      <c r="D11" s="30" t="n">
+      <c r="C11" s="34" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>19.08</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D12" s="30" t="n">
         <v>20</v>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="C14" s="34" t="n">
-        <v>4.25</v>
+        <v>3.46</v>
       </c>
       <c r="D14" s="34" t="n">
         <v>3</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>8</v>
@@ -2106,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2186,17 +2186,17 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -2205,20 +2205,20 @@
         <v>-312</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>272.72</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>-85088.64</v>
-      </c>
-      <c r="H4" s="16" t="inlineStr">
+        <v>269.17</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>-83981.03999999999</v>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>health</t>
         </is>
       </c>
-      <c r="I4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
@@ -2249,10 +2249,10 @@
         <v>82</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1170</v>
+        <v>1169.32</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>95940</v>
+        <v>95884.24000000001</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -2274,41 +2274,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>MS/AWK</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>ODFL/MKTX</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>1758</v>
+        <v>262</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>214.98</v>
+        <v>236.06</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>377934.84</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
+        <v>61847.72</v>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>sensitive_reversal</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2334,17 +2334,17 @@
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-2676</v>
+        <v>-396</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>123.68</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-330967.68</v>
+        <v>122.98</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-48700.08</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>sensitive_reversal</t>
         </is>
       </c>
     </row>
@@ -2362,41 +2362,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/MKTX</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>ODFL/JKHY</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>ODFL</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>228.79</v>
+        <v>236.06</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>59942.98</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+        <v>30215.68</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="I8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>sensitive_reversal</t>
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="inlineStr">
+        <is>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2408,12 +2408,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2422,17 +2422,17 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-396</v>
+        <v>-191</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>123.18</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>-48779.28</v>
+        <v>133.13</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>-25427.83</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>sensitive_reversal</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2450,41 +2450,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/JKHY</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>ODFL</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>128</v>
+        <v>67</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>228.79</v>
+        <v>2125.11</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>29285.12</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>conservative</t>
+        <v>142382.37</v>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2510,17 +2510,17 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-191</v>
+        <v>-23</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>136.03</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>-25981.73</v>
+        <v>618.95</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>-14235.85</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2538,41 +2538,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>PANW/IQV</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>2045.2</v>
+        <v>280.43</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>137028.4</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+        <v>65340.19</v>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>beta_neutral_long_term</t>
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>PANW/IQV</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-23</v>
+        <v>-350</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>602.92</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>-13867.16</v>
+        <v>182.05</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>-63717.5</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2626,41 +2626,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>PANW/IQV</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>KLAC/LOW</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>233</v>
+        <v>42</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>297.18</v>
+        <v>2125.11</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>69242.94</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+        <v>89254.62</v>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>monthly_aligned_windows</t>
+      <c r="I14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>PANW/IQV</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2686,25 +2686,25 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-350</v>
+        <v>-382</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>180.64</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>-63224</v>
+        <v>207.65</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>-79322.3</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2714,41 +2714,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/LOW</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>KLAC</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>FFIV/VLTO</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>FFIV</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>42</v>
+        <v>426</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>2045.2</v>
+        <v>405.66</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>85898.39999999999</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+        <v>172811.16</v>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>aggressive</t>
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17" t="inlineStr">
+        <is>
+          <t>long_term_tilt</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2774,17 +2774,17 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-382</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>206.64</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>-78936.48</v>
+        <v>-665</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>84.67</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>-56305.55</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I17" s="7" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>long_term_tilt</t>
         </is>
       </c>
     </row>
@@ -2802,41 +2802,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>FFIV/VLTO</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>FFIV</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>LRCX/BSX</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>409.13</v>
+        <v>343.71</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>174289.38</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+        <v>148139.01</v>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>long_term_tilt</t>
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="inlineStr">
+        <is>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-665</v>
+        <v>-1706</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>-54815.95</v>
+        <v>47.69</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>-81359.14</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>long_term_tilt</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2890,17 +2890,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>LRCX/BSX</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>LRCX/RMD</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>LRCX</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2909,22 +2909,22 @@
         <v>431</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>334.41</v>
+        <v>343.71</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>144130.71</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
+        <v>148139.01</v>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>aggressive</t>
+      <c r="I20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>fast_rebalance</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>RMD</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>-1706</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>47.68</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>-81342.08</v>
+        <v>-288</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>186.46</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>-53700.48</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -2964,11 +2964,11 @@
         </is>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>fast_rebalance</t>
         </is>
       </c>
     </row>
@@ -2978,41 +2978,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>LRCX/RMD</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>ORCL/LOW</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>ORCL</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>431</v>
+        <v>243</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>334.41</v>
+        <v>230.33</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>144130.71</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+        <v>55970.19</v>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>fast_rebalance</t>
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>fast_strict</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>ORCL/LOW</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>RMD</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3038,17 +3038,17 @@
         </is>
       </c>
       <c r="E23" s="24" t="n">
-        <v>-288</v>
+        <v>-256</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>182.82</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>-52652.16</v>
+        <v>207.65</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>-53158.4</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I23" s="7" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>fast_rebalance</t>
+          <t>fast_strict</t>
         </is>
       </c>
     </row>
@@ -3066,39 +3066,39 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>ORCL/LOW</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>ORCL</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>CSCO/CAG</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>243</v>
+        <v>912</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>244.58</v>
+        <v>126.5</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>59432.94</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
+        <v>115368</v>
+      </c>
+      <c r="H24" s="17" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I24" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>ORCL/LOW</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>CAG</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -3126,13 +3126,13 @@
         </is>
       </c>
       <c r="E25" s="24" t="n">
-        <v>-256</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>206.64</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>-52899.84</v>
+        <v>-4137</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>-52043.46</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
@@ -3154,41 +3154,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>CSCO/CAG</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>NUE/INTU</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>NUE</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>912</v>
+        <v>329</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>128</v>
+        <v>257.73</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>116736</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>fast_strict</t>
+        <v>84793.17</v>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>CAG</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -3214,17 +3214,17 @@
         </is>
       </c>
       <c r="E27" s="24" t="n">
-        <v>-4137</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="G27" s="18" t="n">
-        <v>-53201.82</v>
+        <v>-82</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>311.44</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>-25538.08</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I27" s="7" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>fast_strict</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -3242,41 +3242,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>NUE/INTU</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>NUE</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>CSCO/REGN</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>CSCO</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>329</v>
+        <v>912</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>258.46</v>
+        <v>126.5</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>85033.34</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>conservative</t>
+        <v>115368</v>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -3302,17 +3302,17 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>-82</v>
+        <v>-89</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>322.14</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>-26415.48</v>
+        <v>618.95</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>-55086.55</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I29" s="7" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3330,41 +3330,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>CSCO/REGN</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>CSCO</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>NUE</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>912</v>
+        <v>329</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>128</v>
+        <v>257.73</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>116736</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>monthly_aligned_windows</t>
+        <v>84793.17</v>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="17" t="inlineStr">
+        <is>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3376,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3390,17 +3390,17 @@
         </is>
       </c>
       <c r="E31" s="24" t="n">
-        <v>-89</v>
+        <v>-422</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>602.92</v>
-      </c>
-      <c r="G31" s="18" t="n">
-        <v>-53659.88</v>
+        <v>122.98</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>-51897.56</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I31" s="7" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3418,41 +3418,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>NUE/MKTX</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>NUE</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>STLD/ISRG</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>329</v>
+        <v>502</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>258.46</v>
+        <v>275.13</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>85033.34</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+        <v>138115.26</v>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="I32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
+      <c r="I32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>beta_neutral</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -3478,25 +3478,25 @@
         </is>
       </c>
       <c r="E33" s="24" t="n">
-        <v>-422</v>
+        <v>-79</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>123.18</v>
-      </c>
-      <c r="G33" s="18" t="n">
-        <v>-51981.96</v>
+        <v>407.29</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>-32175.91</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>beta_neutral</t>
         </is>
       </c>
     </row>
@@ -3506,41 +3506,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>STLD/ISRG</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>BWA/VLTO</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>502</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>271.41</v>
+        <v>2359</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>76.55</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>136247.82</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>beta_neutral</t>
+        <v>180581.45</v>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="17" t="inlineStr">
+        <is>
+          <t>kalman_aggressive</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="E35" s="24" t="n">
-        <v>-79</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>402.3</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <v>-31781.7</v>
+        <v>-961</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>84.67</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>-81367.87</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral</t>
+          <t>kalman_aggressive</t>
         </is>
       </c>
     </row>
@@ -3594,41 +3594,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>BWA/VLTO</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>BWA</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>STLD/HII</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>2359</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>74.08</v>
+        <v>502</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>275.13</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>174754.72</v>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>kalman_aggressive</t>
+        <v>138115.26</v>
+      </c>
+      <c r="H36" s="17" t="inlineStr">
+        <is>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -3654,17 +3654,17 @@
         </is>
       </c>
       <c r="E37" s="24" t="n">
-        <v>-961</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>82.43000000000001</v>
-      </c>
-      <c r="G37" s="18" t="n">
-        <v>-79215.23</v>
+        <v>-178</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>287.54</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>-51182.12</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I37" s="7" t="n">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>kalman_aggressive</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -3682,41 +3682,41 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>STLD/HII</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>BWA/CME</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>BWA</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>502</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>271.41</v>
+        <v>2359</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>76.55</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>136247.82</v>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
+        <v>180581.45</v>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t>kalman_aggressive</t>
         </is>
       </c>
     </row>
@@ -3728,12 +3728,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -3742,111 +3742,23 @@
         </is>
       </c>
       <c r="E39" s="24" t="n">
-        <v>-178</v>
+        <v>-298</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>293.66</v>
-      </c>
-      <c r="G39" s="18" t="n">
-        <v>-52271.48</v>
+        <v>252.64</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>-75286.72</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="I39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>BWA/CME</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>BWA</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>2359</v>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>74.08</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>174754.72</v>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="I40" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>kalman_aggressive</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>BWA/CME</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="n">
-        <v>-298</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>250.53</v>
-      </c>
-      <c r="G41" s="18" t="n">
-        <v>-74657.94</v>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>kalman_aggressive</t>
         </is>
@@ -3866,7 +3778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3928,26 +3840,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>CI/MTD</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>12601.74</v>
+        <v>13653.58</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>181028.64</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
+        <v>179865.28</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>vol_agnostic</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t>short</t>
         </is>
@@ -3961,21 +3873,21 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>47056.14</v>
+        <v>13324.02</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>708902.52</v>
+        <v>110547.8</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>sensitive_reversal</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -3990,26 +3902,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>ODFL/MKTX</t>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>ODFL/JKHY</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>11340.08</v>
+        <v>4859.49</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>108722.26</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>sensitive_reversal</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
+        <v>55643.51</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4023,21 +3935,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ODFL/JKHY</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3375.03</v>
+        <v>7979.65</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>55266.85</v>
+        <v>156618.22</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -4052,26 +3964,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/REGN</t>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>PANW/IQV</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2994.37</v>
+        <v>1696.18</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>150895.56</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>beta_neutral_long_term</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
+        <v>129057.69</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4085,21 +3997,21 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>PANW/IQV</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6092.43</v>
+        <v>12217.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>132466.94</v>
+        <v>168576.92</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -4114,26 +4026,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>KLAC/LOW</t>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>9246.9</v>
+        <v>8678.629999999999</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>164834.88</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>aggressive</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
+        <v>229116.71</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>long_term_tilt</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4147,21 +4059,21 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>11646.45</v>
+        <v>12061.15</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>229105.33</v>
+        <v>229498.15</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>long_term_tilt</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -4176,26 +4088,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>LRCX/BSX</t>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>8069.91</v>
+        <v>12187.11</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>225472.79</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>aggressive</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+        <v>201839.49</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>fast_rebalance</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4209,21 +4121,21 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>ORCL/LOW</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9227.129999999999</v>
+        <v>2823.41</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>196782.87</v>
+        <v>109128.59</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>fast_rebalance</t>
+          <t>fast_strict</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -4238,26 +4150,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ORCL/LOW</t>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>6544.72</v>
+        <v>8440.860000000001</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>112332.78</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+        <v>167411.46</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>fast_strict</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4271,21 +4183,21 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8650.5</v>
+        <v>4190.55</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>169937.82</v>
+        <v>110331.25</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>fast_strict</t>
+          <t>conservative</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -4300,26 +4212,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>NUE/INTU</t>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>3553.32</v>
+        <v>5173.83</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>111448.82</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>conservative</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
+        <v>170454.55</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
+        </is>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4333,21 +4245,21 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7968.5</v>
+        <v>5522.49</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>170395.88</v>
+        <v>136690.73</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -4362,26 +4274,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>NUE/MKTX</t>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>5678.26</v>
+        <v>8890.610000000001</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>137015.3</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>weekly_aligned_windows</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
+        <v>170291.17</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>beta_neutral</t>
+        </is>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4395,21 +4307,21 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7417.38</v>
+        <v>9214.26</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>168029.52</v>
+        <v>261949.32</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral</t>
+          <t>kalman_aggressive</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -4424,26 +4336,26 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>BWA/VLTO</t>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>5540.17</v>
+        <v>11192.1</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>253969.95</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>kalman_aggressive</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
+        <v>189297.38</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>weekly_aligned_windows</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4457,55 +4369,24 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>8235.299999999999</v>
+        <v>17787.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>188519.3</v>
+        <v>255868.17</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>kalman_aggressive</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>BWA/CME</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>12589.35</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>249412.66</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>kalman_aggressive</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -4565,12 +4446,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4461,12 @@
           <t>T_1D</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
@@ -4599,12 +4480,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -4614,14 +4495,14 @@
           <t>T_1M</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
@@ -4704,16 +4585,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.24</v>
+        <v>14.44</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-1.43</v>
+        <v>-0.75</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>-16.67</v>
+      <c r="E6" s="22" t="n">
+        <v>-15.18</v>
       </c>
     </row>
     <row r="7">
@@ -4722,17 +4603,17 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="D7" s="16" t="n">
+      <c r="B7" s="17" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>11.9</v>
+      <c r="E7" s="23" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="8">
@@ -4742,16 +4623,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>28.38</v>
+        <v>24.1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6.77</v>
+        <v>3.86</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>-21.61</v>
+      <c r="E8" s="22" t="n">
+        <v>-20.24</v>
       </c>
     </row>
     <row r="9">
@@ -4760,17 +4641,17 @@
           <t>AISS</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>66.95999999999999</v>
-      </c>
-      <c r="D9" s="16" t="n">
+      <c r="B9" s="17" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <v>26.38</v>
+      <c r="E9" s="20" t="n">
+        <v>38.16</v>
       </c>
     </row>
     <row r="11">
@@ -4795,101 +4676,101 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>MS/AWK</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>20.38</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>12.68</v>
+          <t>LRCX/RMD</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>12.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10.08</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>8.07</v>
+          <t>STLD/HII</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>6.63</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>5.75</v>
+          <t>KLAC/LOW</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>4.36</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>4.21</v>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>5.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.02</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>CI/MTD</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>3.92</v>
+          <t>FFIV/VLTO</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>4.44</v>
       </c>
     </row>
     <row r="23">
@@ -4899,47 +4780,47 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>3.36</v>
+          <t>BWA/CME</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>4.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>CI/MTD</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>3.36</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>3.32</v>
+          <t>CSCO/REGN</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>3.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -5049,31 +4930,31 @@
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>38.26</v>
+      <c r="B5" s="21" t="n">
+        <v>38.97</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.006 (t=0.07)</t>
+          <t>0.003 (t=0.04)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>-0.082 (t=-0.61)</t>
+          <t>-0.075 (t=-0.55)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.081 (t=0.67)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -5083,12 +4964,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.101 (t=-0.57)</t>
+          <t>-0.111 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>-0.108 (t=-1.71)</t>
+          <t>-0.11 (t=-1.72)</t>
         </is>
       </c>
     </row>
@@ -5098,46 +4979,46 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>36.87</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E6" s="16" t="n">
+      <c r="B6" s="20" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>0.151 (t=0.82)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>-0.231 (t=-0.81)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>-0.027 (t=-0.11)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>0.33 (t=1.39)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>-0.246 (t=-0.66)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>-0.163 (t=-1.22)</t>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>0.056 (t=0.39)</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>-0.116 (t=-0.52)</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>-0.06 (t=-0.31)</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>0.241 (t=1.31)</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>-0.207 (t=-0.72)</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -5147,46 +5028,46 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
-        <v>44.08</v>
+      <c r="B7" s="21" t="n">
+        <v>28.62</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.2 (t=-0.81)</t>
+          <t>-0.069 (t=-0.42)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>0.156 (t=0.41)</t>
+          <t>-0.004 (t=-0.02)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.19 (t=0.56)</t>
+          <t>0.235 (t=1.04)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.225 (t=-0.71)</t>
+          <t>-0.103 (t=-0.49)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.076 (t=0.15)</t>
+          <t>0.022 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.035 (t=-0.19)</t>
+          <t>-0.065 (t=-0.55)</t>
         </is>
       </c>
     </row>
@@ -5275,10 +5156,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>4.098</v>
+        <v>3.733</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>36.631</v>
+        <v>32.559</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -5287,10 +5168,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.799</v>
+        <v>1.7</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.799</v>
+        <v>1.7</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -5302,26 +5183,26 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>-2.976</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>21.338</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="b">
+      <c r="B5" s="17" t="n">
+        <v>-0.415</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2.311</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>2.031</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>2.346</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.316</v>
+      <c r="F5" s="17" t="n">
+        <v>1.595</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5331,10 +5212,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.153</v>
+        <v>5.366</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>39.334</v>
+        <v>49.493</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -5343,10 +5224,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.15</v>
+        <v>3.763</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.15</v>
+        <v>3.763</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -5411,31 +5292,31 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.775</v>
+        <v>1.889</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.9504</v>
+        <v>0.9591</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>76.7</v>
+        <v>76.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>8.09</v>
+        <v>9.08</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4.04</v>
+        <v>4.54</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>3.365</v>
+        <v>2.736</v>
       </c>
     </row>
     <row r="10">
@@ -5444,32 +5325,32 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0.6757</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>1877</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>0.334</v>
+      <c r="B10" s="17" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>352</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>0.311</v>
       </c>
     </row>
     <row r="11">
@@ -5479,13 +5360,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.464</v>
+        <v>1.314</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.9213</v>
+        <v>0.8929</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>196</v>
+        <v>255</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5494,16 +5375,16 @@
         <v>16.75</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>6.289</v>
+        <v>5.379</v>
       </c>
     </row>
   </sheetData>
@@ -5587,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>461441.55</v>
+        <v>273947.12</v>
       </c>
     </row>
     <row r="6">
@@ -5597,16 +5478,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>1337975.3</v>
+        <v>1004176.17</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>1354215.85</v>
+        <v>1350253.3</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>1079814.64</v>
+        <v>1007658.6</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>624696.51</v>
+        <v>899695.63</v>
       </c>
     </row>
     <row r="7">
@@ -5616,16 +5497,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2402800.18</v>
+        <v>2047699.95</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1942363.18</v>
+        <v>2325374.18</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1507293.2</v>
+        <v>1624155.02</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>582306.3</v>
+        <v>752511.91</v>
       </c>
     </row>
     <row r="8">
@@ -5635,16 +5516,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>3740775.48</v>
+        <v>3051876.12</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3296579.03</v>
+        <v>3675627.49</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2587107.83</v>
+        <v>2631813.62</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1668444.36</v>
+        <v>1926154.66</v>
       </c>
     </row>
     <row r="9">
@@ -5654,467 +5535,467 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1311740.49</v>
+        <v>984486.4399999999</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1327662.6</v>
+        <v>1323777.75</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1058641.8</v>
+        <v>987900.59</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>612447.5600000001</v>
+        <v>882054.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>26234.81</v>
+        <v>958972.4</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>26553.25</v>
+        <v>1252192.38</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>21172.84</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>12248.95</v>
+        <v>646051.79</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1298936.98</v>
+        <v>1943458.84</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>940565.8199999999</v>
+        <v>2575970.13</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>491682.51</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1633952.38</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>882054.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>2636912.28</v>
+        <v>1108417.28</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>2294781.67</v>
+        <v>1099657.36</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1571497.14</v>
+        <v>997861.24</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>624696.51</v>
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1103863.2</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1001797.36</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1015610.69</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1043747.85</v>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2.736</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3.318</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1.566</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>3.365</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>3.264</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>2.526</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>1.145</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>-0.029</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>606437.28</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>729830.39</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>522411.12</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>326913.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>742908.13</v>
+        <v>501980</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>654005.16</v>
+        <v>369826.97</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>513187</v>
+        <v>475450.12</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>238950.77</v>
+        <v>717186.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>360955.07</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>347792.2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>502423.69</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>804797.08</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
         <v>-0</v>
       </c>
-      <c r="D18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>0</v>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>COMBINED — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>COMBINED — 双账户法</t>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1099657.36</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>997861.24</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>752511.91</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>714048.64</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>595057.79</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>596594.65</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>508708.08</v>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>2047699.95</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2325374.18</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1624155.02</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>752511.91</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>2402800.18</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1942363.18</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1507293.2</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>582306.3</v>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>939282.67</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>1225716.82</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>626293.78</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>1688751.54</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>1347305.39</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>910698.55</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>73598.21000000001</v>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1099657.36</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>997861.24</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>752511.91</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>714048.64</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>595057.79</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>596594.65</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>508708.08</v>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>17641.09</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>389814.56</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>406739.57</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>419016.04</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>535039.77</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>17641.09</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>389814.56</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>406739.57</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>419016.04</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>535039.77</v>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>984486.4399999999</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>1323777.75</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>987900.59</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>882054.54</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>1311740.49</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>1327662.6</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>1058641.8</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>612447.5600000001</v>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>984486.4399999999</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>1323777.75</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>987900.59</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>882054.54</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>1311740.49</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1327662.6</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1058641.8</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>612447.5600000001</v>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>19689.73</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>26475.55</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>19758.01</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
-        <v>389814.56</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>406739.57</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>419016.04</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>535039.77</v>
+      <c r="B31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>17641.09</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B32" s="11" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>0</v>
+      <c r="B32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>273947.12</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>1103863.2</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>1001797.36</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>1015610.69</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>1043747.85</v>
+      <c r="B33" s="4" t="n">
+        <v>1108417.28</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1099657.36</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>997861.24</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
+      <c r="B34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6159,16 +6040,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>446084.33</v>
+        <v>480593.83</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>452394.23</v>
+        <v>478778.84</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>443718.3</v>
+        <v>341194.33</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>494353.81</v>
+        <v>513606.13</v>
       </c>
     </row>
     <row r="40">
@@ -6178,16 +6059,16 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>86790.41</v>
+        <v>85660.66</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>89371.34</v>
+        <v>86755.42999999999</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>91093.02</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>228513.46</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>106730.81</v>
       </c>
     </row>
     <row r="41">
@@ -6197,16 +6078,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>95940</v>
+        <v>95884.24000000001</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>90309.06</v>
+        <v>97052.74000000001</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>90453.38</v>
+        <v>221113.56</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>90960.92</v>
+        <v>102242.25</v>
       </c>
     </row>
     <row r="42">
@@ -6216,16 +6097,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>628814.74</v>
+        <v>662138.73</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>632074.63</v>
+        <v>662587.01</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>625264.7</v>
+        <v>790821.35</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>585314.73</v>
+        <v>722579.1899999999</v>
       </c>
     </row>
     <row r="43">
@@ -6235,467 +6116,467 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>85088.64</v>
+        <v>83981.03999999999</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>87618.96000000001</v>
+        <v>85054.34</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>89306.88</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>224032.8</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>104638.05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="n">
-        <v>1701.77</v>
-      </c>
-      <c r="C44" s="13" t="n">
-        <v>1752.38</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>1786.14</v>
-      </c>
-      <c r="E44" s="17" t="n">
+          <t>Margin Loan 保证金借款</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>83981.03999999999</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>85054.34</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>224032.8</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>104638.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>86790.41</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>89371.34</v>
+        <v>577532.67</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>91093.02</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0</v>
+        <v>566788.55</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>617941.14</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="n">
-        <v>542024.33</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>542703.29</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>534171.6800000001</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>585314.73</v>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>0.335</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.155</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>-0.004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>0.155</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>35973.06</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>36421.42</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>89029.27</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>41376.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
+          <t>Excess Liquidity 超额流动性</t>
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>36205.73</v>
+        <v>542184.63</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>35585.6</v>
+        <v>541111.25</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>35952.05</v>
+        <v>477759.28</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>18192.18</v>
+        <v>576565.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n">
-        <v>505818.6</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>507117.69</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>498219.63</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>567122.55</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+      <c r="B51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>MRPT — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>MRPT — 双账户法</t>
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>95884.24000000001</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>97052.74000000001</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>221113.56</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>102242.25</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>287257.39</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>275454.22</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>268789.3</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>585314.73</v>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
-        <v>191317.39</v>
-      </c>
-      <c r="C57" s="13" t="n">
-        <v>185145.16</v>
-      </c>
-      <c r="D57" s="13" t="n">
-        <v>178335.92</v>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>494353.81</v>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>95884.24000000001</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>97052.74000000001</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>221113.56</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>102242.25</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>95940</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>90309.06</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>90453.38</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>90960.92</v>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>95884.24000000001</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>97052.74000000001</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>221113.56</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>102242.25</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>287257.39</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>275454.22</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>268789.3</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>585314.73</v>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>1701.09</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>4480.66</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>2092.76</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="n">
-        <v>254766.94</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>267249.07</v>
-      </c>
-      <c r="D61" s="13" t="n">
-        <v>265382.38</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1701.09</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>4480.66</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>2092.76</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>254766.94</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>267249.07</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>265382.38</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>0</v>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>83981.03999999999</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>85054.34</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>224032.8</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>104638.05</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n">
-        <v>85088.64</v>
-      </c>
-      <c r="C63" s="13" t="n">
-        <v>87618.96000000001</v>
-      </c>
-      <c r="D63" s="13" t="n">
-        <v>89306.88</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0</v>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n">
+        <v>83981.03999999999</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>85054.34</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>224032.8</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>104638.05</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>85088.64</v>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>87618.96000000001</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>89306.88</v>
-      </c>
-      <c r="E64" s="11" t="n">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
-        <v>254766.94</v>
-      </c>
-      <c r="C65" s="13" t="n">
-        <v>267249.07</v>
-      </c>
-      <c r="D65" s="13" t="n">
-        <v>265382.38</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+      <c r="B65" s="4" t="n">
+        <v>1679.62</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>1701.09</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>4480.66</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>2092.76</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>0</v>
+      <c r="B66" s="13" t="n">
+        <v>480593.83</v>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>478778.84</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>341194.33</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>513606.13</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
-        <v>542024.33</v>
-      </c>
-      <c r="C67" s="13" t="n">
-        <v>542703.29</v>
-      </c>
-      <c r="D67" s="13" t="n">
-        <v>534171.6800000001</v>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>585314.73</v>
+      <c r="B67" s="4" t="n">
+        <v>578157.6899999999</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>577532.67</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>566788.55</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>617941.14</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="n">
+      <c r="B68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6759,16 +6640,16 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1251184.89</v>
+        <v>918515.51</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>1264844.51</v>
+        <v>1263497.88</v>
       </c>
       <c r="D74" s="13" t="n">
-        <v>988721.62</v>
+        <v>779145.15</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>624696.51</v>
+        <v>792964.8199999999</v>
       </c>
     </row>
     <row r="75">
@@ -6778,16 +6659,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>2306860.18</v>
+        <v>1951815.71</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1852054.12</v>
+        <v>2228321.44</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1416839.82</v>
+        <v>1403041.46</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>491345.38</v>
+        <v>650269.66</v>
       </c>
     </row>
     <row r="76">
@@ -6797,16 +6678,16 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>3558045.07</v>
+        <v>2870331.22</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>3116898.63</v>
+        <v>3491819.32</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>2405561.44</v>
+        <v>2182186.61</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>1116041.89</v>
+        <v>1443234.48</v>
       </c>
     </row>
     <row r="77">
@@ -6816,467 +6697,467 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>1226651.85</v>
+        <v>900505.4</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1240043.64</v>
+        <v>1238723.41</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>969334.92</v>
+        <v>763867.79</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>612447.5600000001</v>
+        <v>777416.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Short Collateral Due 担保差额 2%</t>
+          <t>Margin Loan 保证金借款</t>
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>24533.04</v>
+        <v>1439566.23</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>24800.87</v>
+        <v>1730971.22</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>19386.7</v>
+        <v>987246.14</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>12248.95</v>
+        <v>239659.01</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Margin Loan 保证金借款</t>
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Total Liabilities 总负债</t>
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>1745021.31</v>
+        <v>2340071.63</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1392960.04</v>
+        <v>2969694.63</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>935400.8100000001</v>
+        <v>1751113.93</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>32912.26</v>
+        <v>1017075.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Total Liabilities 总负债</t>
+          <t>NAV (Equity) 净值 = TA - TL</t>
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>2996206.2</v>
+        <v>530259.59</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>2657804.55</v>
+        <v>522124.69</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>1924122.43</v>
+        <v>431072.68</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>657608.77</v>
+        <v>426158.98</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>NAV (Equity) 净值 = TA - TL</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="n">
-        <v>561838.87</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>459094.08</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>481439.01</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>458433.12</v>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Gross Leverage 总杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>5.379</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>5.027</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Gross Leverage 总杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="n">
-        <v>6.289</v>
-      </c>
-      <c r="C82" s="16" t="n">
-        <v>6.735</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>4.956</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>2.408</v>
+          <t>Net Leverage 净杠杆 (x)</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>1.895</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.298</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Net Leverage 净杠杆 (x)</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="C83" s="7" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E83" s="7" t="n">
-        <v>-0.264</v>
+          <t>PM Requirement (20%)</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n">
+        <v>570464.22</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>693408.97</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>433381.85</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>285537.23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>PM Requirement (20%)</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>706702.41</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>618419.55</v>
-      </c>
-      <c r="D84" s="13" t="n">
-        <v>477234.95</v>
+          <t>Excess Liquidity 超额流动性</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="n">
+        <v>-40204.63</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>-171284.28</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>-2309.17</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>220758.59</v>
+        <v>140621.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Excess Liquidity 超额流动性</t>
-        </is>
-      </c>
-      <c r="B85" s="18" t="n">
-        <v>-144863.54</v>
-      </c>
-      <c r="C85" s="18" t="n">
-        <v>-159325.47</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>4204.06</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>237674.53</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
           <t>Balance Check (≈0)</t>
         </is>
       </c>
-      <c r="B86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0</v>
+      <c r="B85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>MTFS — 双账户法</t>
+        </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>MTFS — 双账户法</t>
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>T (今日)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>T-1D (前日)</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>T-1W (上周)</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>T-1M (上月)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>T (今日)</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>T-1D (前日)</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>T-1W (上周)</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>T-1M (上月)</t>
-        </is>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>522124.69</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>431072.68</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>426158.98</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>366797.6</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>274980.66</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>285864.21</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>204068.16</v>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Cash 现金</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Cash 现金</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Long Book — Market Value 市值</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="n">
+        <v>1951815.71</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>2228321.44</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1403041.46</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>650269.66</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Long Book — Market Value 市值</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>2306860.18</v>
-      </c>
-      <c r="C92" s="4" t="n">
-        <v>1852054.12</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>1416839.82</v>
-      </c>
-      <c r="E92" s="4" t="n">
-        <v>491345.38</v>
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Long Book — Margin Loan 融资</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>1421556.12</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>1706196.75</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>971968.78</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>224110.68</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>Long Book — Margin Loan 融资</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>1940062.58</v>
-      </c>
-      <c r="C93" s="13" t="n">
-        <v>1577073.46</v>
-      </c>
-      <c r="D93" s="13" t="n">
-        <v>1130975.61</v>
-      </c>
-      <c r="E93" s="13" t="n">
-        <v>287277.22</v>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Long Book — NAV</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>522124.69</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>431072.68</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>426158.98</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>Long Book — NAV</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>366797.6</v>
-      </c>
-      <c r="C94" s="4" t="n">
-        <v>274980.66</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>285864.21</v>
-      </c>
-      <c r="E94" s="4" t="n">
-        <v>204068.16</v>
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Allocated Capital 分配资本</t>
+        </is>
+      </c>
+      <c r="B94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Allocated Capital 分配资本</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="n">
-        <v>195041.27</v>
-      </c>
-      <c r="C95" s="13" t="n">
-        <v>184113.42</v>
-      </c>
-      <c r="D95" s="13" t="n">
-        <v>195574.8</v>
-      </c>
-      <c r="E95" s="13" t="n">
-        <v>254364.96</v>
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Collateral 担保金</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Collateral 担保金</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>195041.27</v>
-      </c>
-      <c r="C96" s="4" t="n">
-        <v>184113.42</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>195574.8</v>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>254364.96</v>
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Short Proceeds 做空收入</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>900505.4</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>1238723.41</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>763867.79</v>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>777416.49</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>Short Book — Short Proceeds 做空收入</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="n">
-        <v>1226651.85</v>
-      </c>
-      <c r="C97" s="13" t="n">
-        <v>1240043.64</v>
-      </c>
-      <c r="D97" s="13" t="n">
-        <v>969334.92</v>
-      </c>
-      <c r="E97" s="13" t="n">
-        <v>612447.5600000001</v>
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Short Book — Market Value 市值(负债)</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="n">
+        <v>900505.4</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>1238723.41</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>763867.79</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>777416.49</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Short Book — Market Value 市值(负债)</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>1226651.85</v>
-      </c>
-      <c r="C98" s="4" t="n">
-        <v>1240043.64</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>969334.92</v>
-      </c>
-      <c r="E98" s="4" t="n">
-        <v>612447.5600000001</v>
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Short Book — Margin Loan 融资(2%)</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>18010.11</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>24774.47</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>15277.36</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>15548.33</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B99" s="13" t="n">
-        <v>195041.27</v>
-      </c>
-      <c r="C99" s="13" t="n">
-        <v>184113.42</v>
-      </c>
-      <c r="D99" s="13" t="n">
-        <v>195574.8</v>
-      </c>
-      <c r="E99" s="13" t="n">
-        <v>254364.96</v>
+      <c r="B99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="12" t="inlineStr">
         <is>
           <t>Unallocated Cash 未分配现金</t>
         </is>
       </c>
-      <c r="B100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="11" t="n">
+      <c r="B100" s="15" t="n">
         <v>-0</v>
       </c>
-      <c r="D100" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="11" t="n">
+      <c r="C100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>Dual-View NAV 双账户法NAV</t>
         </is>
       </c>
-      <c r="B101" s="13" t="n">
-        <v>561838.87</v>
-      </c>
-      <c r="C101" s="13" t="n">
-        <v>459094.08</v>
-      </c>
-      <c r="D101" s="13" t="n">
-        <v>481439.01</v>
-      </c>
-      <c r="E101" s="13" t="n">
-        <v>458433.12</v>
+      <c r="B101" s="4" t="n">
+        <v>530259.59</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>522124.69</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>431072.68</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>426158.98</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>NAV Alignment Check (≈0)</t>
         </is>
       </c>
-      <c r="B102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="7" t="n">
+      <c r="B102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7346,22 +7227,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>102065.84</v>
+        <v>8759.92</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>88252.50999999999</v>
+        <v>110556.04</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>60115.35</v>
+        <v>64317.16</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>182364.41</v>
+        <v>186918.49</v>
       </c>
     </row>
     <row r="6">
@@ -7371,16 +7252,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>177.94</v>
+        <v>131.37</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>889.6799999999999</v>
+        <v>656.83</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>3736.67</v>
+        <v>2758.69</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>25978.74</v>
+        <v>19310.81</v>
       </c>
     </row>
     <row r="7">
@@ -7390,7 +7271,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>187827.68</v>
+        <v>159892.52</v>
       </c>
     </row>
     <row r="9">
@@ -7428,22 +7309,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
-        <v>-678.96</v>
+      <c r="B11" s="4" t="n">
+        <v>625.02</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7852.65</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>-43290.4</v>
+        <v>11369.14</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>-39783.45</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>32692.39</v>
+        <v>68825.75</v>
       </c>
     </row>
     <row r="12">
@@ -7452,16 +7333,16 @@
           <t>Interest expense (est)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
+      <c r="B12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7472,7 +7353,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>12601.74</v>
+        <v>13653.58</v>
       </c>
     </row>
     <row r="15">
@@ -7510,22 +7391,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>102744.79</v>
+        <v>8134.9</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>80399.86</v>
+        <v>99186.91</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>103405.75</v>
+        <v>104100.61</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>149672.02</v>
+        <v>118092.74</v>
       </c>
     </row>
     <row r="18">
@@ -7535,16 +7416,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>239.04</v>
+        <v>197.2</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>1195.22</v>
+        <v>986</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>5019.92</v>
+        <v>4141.22</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>34900.43</v>
+        <v>28988.53</v>
       </c>
     </row>
     <row r="19">
@@ -7554,7 +7435,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>175225.94</v>
+        <v>146238.94</v>
       </c>
     </row>
     <row r="21">
@@ -7630,19 +7511,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1099657.36</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1015610.69</v>
+        <v>997861.24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1043747.85</v>
+        <v>1044100.12</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7655,16 +7536,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>102065.84</v>
+        <v>8759.92</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>88252.50999999999</v>
+        <v>110556.04</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>60115.35</v>
+        <v>64317.16</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>182364.41</v>
+        <v>186918.49</v>
       </c>
     </row>
     <row r="7">
@@ -7692,36 +7573,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
+      <c r="B8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
     </row>
     <row r="10">
@@ -7730,17 +7611,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>19.79</v>
+      <c r="B10" s="20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>20.28</v>
       </c>
     </row>
     <row r="11">
@@ -7749,17 +7630,17 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-5.58</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-9.57</v>
+      <c r="B11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -7797,19 +7678,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>542703.29</v>
+        <v>577532.67</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>534171.6800000001</v>
+        <v>566788.55</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>585314.73</v>
+        <v>617941.14</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7821,17 +7702,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>-678.96</v>
+      <c r="B16" s="13" t="n">
+        <v>625.02</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>7852.65</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-43290.4</v>
+        <v>11369.14</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>-39783.45</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>32692.39</v>
+        <v>68825.75</v>
       </c>
     </row>
     <row r="17">
@@ -7859,36 +7740,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17" t="n">
+      <c r="B18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>542024.33</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>542024.33</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>542024.33</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>542024.33</v>
+        <v>578157.6899999999</v>
       </c>
     </row>
     <row r="20">
@@ -7897,17 +7778,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>1.47</v>
+      <c r="B20" s="20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>2.01</v>
       </c>
       <c r="D20" s="23" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>6.42</v>
+        <v>-6.44</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>13.51</v>
       </c>
     </row>
     <row r="21">
@@ -7917,16 +7798,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="22" t="n">
         <v>-0.13</v>
       </c>
-      <c r="C21" s="21" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>-11.77</v>
+      <c r="D21" s="22" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -7964,19 +7845,19 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Beginning NAV</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>459094.08</v>
+        <v>522124.69</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>481439.01</v>
+        <v>431072.68</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>458433.12</v>
+        <v>426158.98</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7989,16 +7870,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>102744.79</v>
+        <v>8134.9</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>80399.86</v>
+        <v>99186.91</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>103405.75</v>
+        <v>104100.61</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>149672.02</v>
+        <v>118092.74</v>
       </c>
     </row>
     <row r="27">
@@ -8026,36 +7907,36 @@
           <t>Withdrawals</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17" t="n">
+      <c r="B28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Ending NAV</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>561838.87</v>
+        <v>530259.59</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>561838.87</v>
+        <v>530259.59</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>561838.87</v>
+        <v>530259.59</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>561838.87</v>
+        <v>530259.59</v>
       </c>
     </row>
     <row r="30">
@@ -8064,17 +7945,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
-        <v>22.38</v>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>36.31</v>
+      <c r="B30" s="20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>28.65</v>
       </c>
     </row>
     <row r="31">
@@ -8083,16 +7964,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="21" t="n">
+      <c r="B31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="D31" s="22" t="n">
         <v>-7.46</v>
       </c>
-      <c r="D31" s="21" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="22" t="n">
         <v>-16.75</v>
       </c>
     </row>
@@ -8143,7 +8024,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>88252.50999999999</v>
+        <v>110556.04</v>
       </c>
     </row>
     <row r="5">
@@ -8152,8 +8033,8 @@
           <t>Investing cash flow</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>-642408.29</v>
+      <c r="B5" s="19" t="n">
+        <v>-426959.08</v>
       </c>
     </row>
     <row r="6">
@@ -8163,7 +8044,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>807254.47</v>
+        <v>312920.61</v>
       </c>
     </row>
     <row r="7">
@@ -8172,8 +8053,8 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>253098.69</v>
+      <c r="B7" s="19" t="n">
+        <v>-3482.43</v>
       </c>
     </row>
     <row r="8">
@@ -8217,7 +8098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9170,7 +9051,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1010661.06</v>
+        <v>1011218.51</v>
       </c>
     </row>
     <row r="97">
@@ -9180,7 +9061,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1023679.41</v>
+        <v>1025407</v>
       </c>
     </row>
     <row r="98">
@@ -9190,7 +9071,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1025724.19</v>
+        <v>1026941.31</v>
       </c>
     </row>
     <row r="99">
@@ -9200,7 +9081,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015750.02</v>
+        <v>1015258.85</v>
       </c>
     </row>
     <row r="100">
@@ -9210,7 +9091,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003777.26</v>
+        <v>1003003.03</v>
       </c>
     </row>
     <row r="101">
@@ -9220,7 +9101,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1014086.2</v>
+        <v>1013068.4</v>
       </c>
     </row>
     <row r="102">
@@ -9230,7 +9111,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1028383.17</v>
+        <v>1026667.89</v>
       </c>
     </row>
     <row r="103">
@@ -9240,7 +9121,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1057042.21</v>
+        <v>1053397.75</v>
       </c>
     </row>
     <row r="104">
@@ -9250,7 +9131,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1054438.15</v>
+        <v>1050736.08</v>
       </c>
     </row>
     <row r="105">
@@ -9260,7 +9141,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1052315.58</v>
+        <v>1049499.07</v>
       </c>
     </row>
     <row r="106">
@@ -9270,7 +9151,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1051354.61</v>
+        <v>1049134.93</v>
       </c>
     </row>
     <row r="107">
@@ -9280,7 +9161,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1044479.78</v>
+        <v>1042919.9</v>
       </c>
     </row>
     <row r="108">
@@ -9290,7 +9171,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1050335.11</v>
+        <v>1048685.92</v>
       </c>
     </row>
     <row r="109">
@@ -9300,7 +9181,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1044442.91</v>
+        <v>1042773.4</v>
       </c>
     </row>
     <row r="110">
@@ -9310,7 +9191,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1046176.28</v>
+        <v>1044235.83</v>
       </c>
     </row>
     <row r="111">
@@ -9320,7 +9201,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1072213.58</v>
+        <v>1070354.14</v>
       </c>
     </row>
     <row r="112">
@@ -9330,7 +9211,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1063030.61</v>
+        <v>1061514.84</v>
       </c>
     </row>
     <row r="113">
@@ -9340,7 +9221,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1075175.58</v>
+        <v>1074870.62</v>
       </c>
     </row>
     <row r="114">
@@ -9350,7 +9231,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080207.25</v>
+        <v>1080512.52</v>
       </c>
     </row>
     <row r="115">
@@ -9360,7 +9241,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1085910.78</v>
+        <v>1086924.48</v>
       </c>
     </row>
     <row r="116">
@@ -9370,7 +9251,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1072326.04</v>
+        <v>1071780.32</v>
       </c>
     </row>
     <row r="117">
@@ -9380,7 +9261,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065410.49</v>
+        <v>1065526.09</v>
       </c>
     </row>
     <row r="118">
@@ -9390,7 +9271,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1079552.28</v>
+        <v>1080594.32</v>
       </c>
     </row>
     <row r="119">
@@ -9400,7 +9281,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1073850.36</v>
+        <v>1075591.99</v>
       </c>
     </row>
     <row r="120">
@@ -9410,7 +9291,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1068923.8</v>
+        <v>1071013.67</v>
       </c>
     </row>
     <row r="121">
@@ -9420,7 +9301,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1071061.15</v>
+        <v>1073689.47</v>
       </c>
     </row>
     <row r="122">
@@ -9430,7 +9311,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1071649.93</v>
+        <v>1074236.64</v>
       </c>
     </row>
     <row r="123">
@@ -9440,7 +9321,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1081609.49</v>
+        <v>1084547.15</v>
       </c>
     </row>
     <row r="124">
@@ -9450,7 +9331,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1082665.34</v>
+        <v>1085528.37</v>
       </c>
     </row>
     <row r="125">
@@ -9460,7 +9341,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1089743.49</v>
+        <v>1092616.33</v>
       </c>
     </row>
     <row r="126">
@@ -9470,7 +9351,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1089711.86</v>
+        <v>1092781.06</v>
       </c>
     </row>
     <row r="127">
@@ -9480,7 +9361,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1047267.39</v>
+        <v>1053336.82</v>
       </c>
     </row>
     <row r="128">
@@ -9490,7 +9371,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1043747.85</v>
+        <v>1049687.33</v>
       </c>
     </row>
     <row r="129">
@@ -9500,7 +9381,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1038522.14</v>
+        <v>1044100.12</v>
       </c>
     </row>
     <row r="130">
@@ -9510,7 +9391,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1027387.75</v>
+        <v>1032626.83</v>
       </c>
     </row>
     <row r="131">
@@ -9520,7 +9401,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1034795.94</v>
+        <v>1039700.39</v>
       </c>
     </row>
     <row r="132">
@@ -9530,7 +9411,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1032907.49</v>
+        <v>1037551.62</v>
       </c>
     </row>
     <row r="133">
@@ -9540,7 +9421,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1015331.02</v>
+        <v>1019311.74</v>
       </c>
     </row>
     <row r="134">
@@ -9550,7 +9431,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1010937.91</v>
+        <v>1014163.76</v>
       </c>
     </row>
     <row r="135">
@@ -9560,7 +9441,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>996866.8</v>
+        <v>999293.04</v>
       </c>
     </row>
     <row r="136">
@@ -9570,7 +9451,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1008057.17</v>
+        <v>1011409.78</v>
       </c>
     </row>
     <row r="137">
@@ -9580,7 +9461,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1010905.61</v>
+        <v>1014540.8</v>
       </c>
     </row>
     <row r="138">
@@ -9590,7 +9471,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1008270.67</v>
+        <v>1011881.11</v>
       </c>
     </row>
     <row r="139">
@@ -9600,7 +9481,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>995181.03</v>
+        <v>998415.39</v>
       </c>
     </row>
     <row r="140">
@@ -9610,7 +9491,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1012313.28</v>
+        <v>1014351.76</v>
       </c>
     </row>
     <row r="141">
@@ -9620,7 +9501,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1021177.12</v>
+        <v>1023498.77</v>
       </c>
     </row>
     <row r="142">
@@ -9630,7 +9511,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1022017.19</v>
+        <v>1023696.66</v>
       </c>
     </row>
     <row r="143">
@@ -9640,7 +9521,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>993609.49</v>
+        <v>996887.45</v>
       </c>
     </row>
     <row r="144">
@@ -9650,7 +9531,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1015610.69</v>
+        <v>1016573.57</v>
       </c>
     </row>
     <row r="145">
@@ -9660,7 +9541,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>995802</v>
+        <v>997861.24</v>
       </c>
     </row>
     <row r="146">
@@ -9670,7 +9551,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>988320.51</v>
+        <v>991493.7</v>
       </c>
     </row>
     <row r="147">
@@ -9680,7 +9561,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>985468.92</v>
+        <v>989347.35</v>
       </c>
     </row>
     <row r="148">
@@ -9690,7 +9571,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1001797.36</v>
+        <v>1004898.62</v>
       </c>
     </row>
     <row r="149">
@@ -9700,7 +9581,17 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1103863.2</v>
+        <v>1099657.36</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n">
+        <v>1108417.28</v>
       </c>
     </row>
   </sheetData>
@@ -9805,34 +9696,34 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1103863.2</v>
+        <v>1108417.28</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2402800.18</v>
+        <v>2047699.95</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1311740.49</v>
+        <v>984486.4399999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3714540.67</v>
+        <v>3032186.39</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1091059.69</v>
+        <v>1063213.51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>3.365</v>
+        <v>2.736</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.988</v>
+        <v>0.959</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>336.5</v>
+        <v>273.56</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>168.25</v>
+        <v>136.78</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -9842,31 +9733,31 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>542024.33</v>
+        <v>578157.6899999999</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>95940</v>
+        <v>95884.24000000001</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>85088.64</v>
+        <v>83981.03999999999</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>181028.64</v>
+        <v>179865.28</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>10851.36</v>
+        <v>11903.2</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.334</v>
+        <v>0.311</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>33.4</v>
+        <v>31.11</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>16.7</v>
+        <v>15.56</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>1</v>
@@ -9879,34 +9770,34 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>561838.87</v>
+        <v>530259.59</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2306860.18</v>
+        <v>1951815.71</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1226651.85</v>
+        <v>900505.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3533512.03</v>
+        <v>2852321.11</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1080208.33</v>
+        <v>1051310.31</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>6.289</v>
+        <v>5.379</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.923</v>
+        <v>1.983</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>628.92</v>
+        <v>537.91</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>314.46</v>
+        <v>268.96</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -9923,7 +9814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9944,7 +9835,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.0762  ·  effective N pairs=13.1  ·  max pair=19.08% of gross</t>
+          <t>HHI=0.0611  ·  effective N pairs=16.4  ·  max pair=8.64% of gross</t>
         </is>
       </c>
     </row>
@@ -9983,42 +9874,42 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>377934.84</v>
+        <v>361162.9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>377934.84</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>10.17</v>
+        <v>361162.9</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>32.58</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>11.91</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>349509.44</v>
+        <v>296278.02</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>349509.44</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>9.41</v>
+        <v>296278.02</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>9.77</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -10027,42 +9918,42 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>330967.68</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>-330967.68</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>8.91</v>
+        <v>276230.52</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>276230.52</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>9.109999999999999</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>288261.42</v>
+        <v>231636.99</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>288261.42</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>7.76</v>
+        <v>231636.99</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>7.64</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>2</v>
@@ -10071,20 +9962,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>272495.64</v>
+        <v>230736</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>272495.64</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>7.34</v>
+        <v>230736</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>7.61</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>2</v>
@@ -10093,42 +9984,42 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>233472</v>
+        <v>172811.16</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>233472</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>6.29</v>
+        <v>172811.16</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>5.7</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>222926.8</v>
+        <v>169586.34</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>222926.8</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>6</v>
+        <v>169586.34</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>5.59</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>2</v>
@@ -10137,42 +10028,42 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>174289.38</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>174289.38</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>4.69</v>
+        <v>137673.42</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>-137673.42</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>4.54</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>170066.68</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>170066.68</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>4.58</v>
+        <v>132480.7</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>-132480.7</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>4.37</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>2</v>
@@ -10181,20 +10072,20 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>134031.18</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>-134031.18</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>3.61</v>
+        <v>100597.64</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>-100597.64</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>3.32</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>2</v>
@@ -10241,16 +10132,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1047625.48</v>
+        <v>1052772.55</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>127176.72</v>
+        <v>126135.72</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>920448.76</v>
+        <v>926636.83</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>24.78</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="21">
@@ -10260,16 +10151,16 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>442562.32</v>
-      </c>
-      <c r="C21" s="17" t="n">
+        <v>445816.86</v>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>442562.32</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>11.91</v>
+        <v>445816.86</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="22">
@@ -10279,16 +10170,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>95940</v>
+        <v>95884.24000000001</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>515646.8</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>-419706.8</v>
+        <v>521929.89</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>-426045.65</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-11.3</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="23">
@@ -10298,35 +10189,35 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>438737.54</v>
+        <v>453226.3</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>52271.48</v>
+        <v>51182.12</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>386466.06</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>10.4</v>
+        <v>402044.18</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>13.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>330967.68</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>-330967.68</v>
+        <v>184524.16</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>-184524.16</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-8.91</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="25">
@@ -10335,36 +10226,17 @@
           <t>finance</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
-        <v>377934.84</v>
+      <c r="B25" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>100639.67</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>277295.17</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>185038.14</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>-185038.14</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>-4.98</v>
+        <v>100714.55</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>-100714.55</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-3.32</v>
       </c>
     </row>
   </sheetData>
@@ -10381,7 +10253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10402,7 +10274,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2.391</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="4">
@@ -10412,7 +10284,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3.354</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="5">
@@ -10422,7 +10294,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>97.86</v>
+        <v>94.84999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -10462,8 +10334,8 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>24.78</v>
+      <c r="B10" s="21" t="n">
+        <v>30.56</v>
       </c>
     </row>
     <row r="11">
@@ -10472,8 +10344,8 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
-        <v>11.91</v>
+      <c r="B11" s="20" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="12">
@@ -10482,8 +10354,8 @@
           <t>health</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
-        <v>-11.3</v>
+      <c r="B12" s="22" t="n">
+        <v>-14.05</v>
       </c>
     </row>
     <row r="13">
@@ -10492,18 +10364,18 @@
           <t>industrial</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
-        <v>10.4</v>
+      <c r="B13" s="20" t="n">
+        <v>13.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>utilities</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n">
-        <v>-8.91</v>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>-6.09</v>
       </c>
     </row>
     <row r="15">
@@ -10512,18 +10384,8 @@
           <t>finance</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n">
-        <v>-4.98</v>
+      <c r="B15" s="23" t="n">
+        <v>-3.32</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-03  ·  Generated 2026-06-10T09:47:13  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-03  ·  Generated 2026-06-24T18:50:02  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.736</v>
+        <v>4.616</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>0.959</v>
+      <c r="B6" s="5" t="n">
+        <v>2.84</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.833</v>
+        <v>5.762</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38394.23</v>
+        <v>111661.88</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3.46</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>33.43</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.889</v>
+        <v>1.888</v>
       </c>
     </row>
     <row r="12">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>9.08 / 4.54</t>
+          <t>9.06 / 4.53</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2.736</v>
+        <v>4.616</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>BWA (32.58% NAV)</t>
+          <t>KLAC (208.95% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>30.56</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>38394.23</v>
+        <v>111661.88</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>54288.74</v>
+        <v>157887.86</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>370510.33</v>
+        <v>1077554.62</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>33.43</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26685.64</v>
+        <v>81798.92</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28974.03</v>
+        <v>97861.73</v>
       </c>
     </row>
     <row r="10">
@@ -1024,157 +1024,157 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5927.26</v>
+        <v>53536.23</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15.44</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4816.52</v>
+        <v>32953.32</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>12.54</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3890.43</v>
+        <v>5801.84</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>3182.2</v>
+        <v>4958.97</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>8.289999999999999</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2784.76</v>
+        <v>2016.79</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.25</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>2127.92</v>
+        <v>1909.68</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>5.54</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>2056.89</v>
+        <v>1566.85</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>2008.59</v>
+        <v>1539.34</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>5.23</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1774.32</v>
+        <v>1535.35</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>4.62</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1703.79</v>
+        <v>1399.55</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>4.44</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1687.93</v>
+        <v>1365.52</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1647.3</v>
+        <v>1087.79</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>4.29</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24">
@@ -1184,36 +1184,36 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>1455.49</v>
+        <v>646.25</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3.79</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>1348.72</v>
+        <v>502.56</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>3.51</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>808.65</v>
+        <v>475.25</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>2.11</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -1418,8 +1418,8 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>67</v>
+      <c r="C12" s="4" t="n">
+        <v>670</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>1015148</v>
@@ -1502,8 +1502,8 @@
           <t>KLAC/LOW</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>42</v>
+      <c r="C16" s="4" t="n">
+        <v>420</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>1015148</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-101586.44</v>
+        <v>-319375.57</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-9.17</v>
+        <v>-28.81</v>
       </c>
     </row>
     <row r="5">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-203172.89</v>
+        <v>-638751.15</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-18.33</v>
+        <v>-57.62</v>
       </c>
     </row>
     <row r="6">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-101586.44</v>
+        <v>-319375.57</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-9.17</v>
+        <v>-28.81</v>
       </c>
     </row>
     <row r="7">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-92663.67999999999</v>
+        <v>-301136.97</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-8.359999999999999</v>
+        <v>-27.16</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>5.38</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.98</v>
+        <v>5.9</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>32.58</v>
+        <v>208.95</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>26.73</v>
+        <v>32.58</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1915,80 +1915,80 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="D10" s="34" t="n">
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>26.73</v>
+      </c>
+      <c r="D10" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="34" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>sector_net</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>sector_net</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1.83</v>
+        <v>5.76</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2019,28 +2019,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="31" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="34" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="D14" s="34" t="n">
+      <c r="C14" s="32" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="D14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>2125.11</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>142382.37</v>
+        <v>1423823.7</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>42</v>
+        <v>420</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>2125.11</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>89254.62</v>
+        <v>892546.2</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7979.65</v>
+        <v>1289420.98</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>156618.22</v>
+        <v>1438059.55</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12217.3</v>
+        <v>815508.88</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>168576.92</v>
+        <v>971868.5</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
@@ -4585,16 +4585,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.44</v>
+        <v>14.76</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>-0.75</v>
+        <v>-0.62</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-15.18</v>
+        <v>-15.38</v>
       </c>
     </row>
     <row r="7">
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>13.24</v>
+        <v>13.59</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>10.5</v>
+        <v>14.38</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>-2.74</v>
+      <c r="E7" s="20" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="8">
@@ -4623,16 +4623,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.1</v>
+        <v>24.67</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.86</v>
+        <v>4.79</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-20.24</v>
+        <v>-19.88</v>
       </c>
     </row>
     <row r="9">
@@ -4642,16 +4642,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>48.22</v>
+        <v>46.98</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>86.38</v>
+        <v>81.45</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>38.16</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="11">
@@ -4676,71 +4676,71 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>15.44</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>12.54</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>10.13</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>8.289999999999999</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.25</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>5.54</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>5.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20">
@@ -4750,47 +4750,47 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>5.23</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4.62</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>4.44</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>4.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>4.29</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="25">
@@ -4800,27 +4800,27 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>3.79</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>3.51</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>2.11</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -4993,27 +4993,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -5042,32 +5042,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>3.733</v>
+        <v>3.744</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>32.559</v>
+        <v>32.684</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -5168,10 +5168,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.7</v>
+        <v>1.703</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.7</v>
+        <v>1.703</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.415</v>
+        <v>-0.453</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.311</v>
+        <v>2.443</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.595</v>
+        <v>1.603</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.665</v>
+        <v>1.681</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="6">
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5.366</v>
+        <v>5.35</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>49.493</v>
+        <v>49.111</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -5224,10 +5224,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3.763</v>
+        <v>3.77</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>3.763</v>
+        <v>3.77</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.889</v>
+        <v>1.888</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0.9591</v>
@@ -5310,13 +5310,13 @@
         <v>76.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>9.08</v>
+        <v>9.06</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>2.736</v>
+        <v>4.616</v>
       </c>
     </row>
     <row r="10">
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.425</v>
+        <v>1.401</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8548</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>8.65</v>
@@ -5344,13 +5344,13 @@
         <v>76.2</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>6.87</v>
+        <v>6.7</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="11">
@@ -5360,13 +5360,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.314</v>
+        <v>1.322</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.8929</v>
+        <v>0.8944</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.04</v>
@@ -5378,13 +5378,13 @@
         <v>79.59999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>1.55</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5.379</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>273947.12</v>
+        <v>273783.06</v>
       </c>
     </row>
     <row r="6">
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2047699.95</v>
+        <v>4132432.86</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2325374.18</v>
+        <v>4228553.42</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1624155.02</v>
+        <v>4049891.36</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>752511.91</v>
@@ -5516,16 +5516,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>3051876.12</v>
+        <v>5136609.03</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>3675627.49</v>
+        <v>5578806.73</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>2631813.62</v>
+        <v>5057549.96</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1926154.66</v>
+        <v>1925990.6</v>
       </c>
     </row>
     <row r="9">
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>958972.4</v>
+        <v>3043564.54</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>1252192.38</v>
+        <v>3155247.92</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>646051.79</v>
+        <v>3071848.7</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1943458.84</v>
+        <v>4028050.98</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2575970.13</v>
+        <v>4479025.67</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1633952.38</v>
+        <v>4059749.29</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>882054.54</v>
@@ -5592,16 +5592,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="13">
@@ -5611,13 +5611,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>2.736</v>
+        <v>4.616</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>3.318</v>
+        <v>5.049</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.618</v>
+        <v>5.049</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.566</v>
@@ -5630,13 +5630,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.959</v>
+        <v>2.84</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.911</v>
+        <v>2.641</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.638</v>
+        <v>3.069</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.124</v>
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>606437.28</v>
+        <v>1023383.86</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>729830.39</v>
+        <v>1110466.23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>522411.12</v>
+        <v>1007558.39</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>326913.29</v>
@@ -5668,16 +5668,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>501980</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>369826.97</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>475450.12</v>
+        <v>85174.19</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>-10685.17</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>-9757.719999999999</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>717186.83</v>
+        <v>717022.77</v>
       </c>
     </row>
     <row r="17">
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -5740,13 +5740,13 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>752511.91</v>
@@ -5778,13 +5778,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>2047699.95</v>
+        <v>4132432.86</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2325374.18</v>
+        <v>4228553.42</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1624155.02</v>
+        <v>4049891.36</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>752511.91</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>939282.67</v>
+        <v>3023874.81</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>1225716.82</v>
+        <v>3128772.36</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>626293.78</v>
+        <v>3052090.69</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -5816,13 +5816,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>752511.91</v>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>273947.12</v>
+        <v>273783.06</v>
       </c>
     </row>
     <row r="33">
@@ -5968,16 +5968,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="34">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>480593.83</v>
+        <v>479548.34</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>478778.84</v>
+        <v>477734.47</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>341194.33</v>
+        <v>340169.4</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>513606.13</v>
+        <v>512488.7</v>
       </c>
     </row>
     <row r="40">
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>662138.73</v>
+        <v>661093.24</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>662587.01</v>
+        <v>661542.64</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>790821.35</v>
+        <v>789796.42</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>722579.1899999999</v>
+        <v>721461.76</v>
       </c>
     </row>
     <row r="43">
@@ -6173,16 +6173,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>566788.55</v>
+        <v>565763.62</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>617941.14</v>
+        <v>616823.71</v>
       </c>
     </row>
     <row r="47">
@@ -6192,13 +6192,13 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>0.335</v>
@@ -6249,16 +6249,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>542184.63</v>
+        <v>541139.14</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>541111.25</v>
+        <v>540066.88</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>477759.28</v>
+        <v>476734.35</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>576565.08</v>
+        <v>575447.65</v>
       </c>
     </row>
     <row r="51">
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>480593.83</v>
+        <v>479548.34</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>478778.84</v>
+        <v>477734.47</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>341194.33</v>
+        <v>340169.4</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>513606.13</v>
+        <v>512488.7</v>
       </c>
     </row>
     <row r="67">
@@ -6549,16 +6549,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>566788.55</v>
+        <v>565763.62</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>617941.14</v>
+        <v>616823.71</v>
       </c>
     </row>
     <row r="68">
@@ -6659,13 +6659,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>1951815.71</v>
+        <v>4036548.62</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2228321.44</v>
+        <v>4131500.68</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1403041.46</v>
+        <v>3828777.8</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>650269.66</v>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>2870331.22</v>
+        <v>4955064.13</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>3491819.32</v>
+        <v>5394998.56</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>2182186.61</v>
+        <v>4607922.95</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1443234.48</v>
@@ -6716,16 +6716,16 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>1439566.23</v>
+        <v>3523112.88</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>1730971.22</v>
+        <v>3632982.4</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>987246.14</v>
+        <v>3412018.11</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>239659.01</v>
+        <v>238705.63</v>
       </c>
     </row>
     <row r="79">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>2340071.63</v>
+        <v>4423618.28</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2969694.63</v>
+        <v>4871705.81</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1751113.93</v>
+        <v>4175885.9</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1017075.5</v>
+        <v>1016122.12</v>
       </c>
     </row>
     <row r="80">
@@ -6754,16 +6754,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>431072.68</v>
+        <v>432037.05</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>426158.98</v>
+        <v>427112.36</v>
       </c>
     </row>
     <row r="81">
@@ -6773,16 +6773,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>5.379</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>6.64</v>
+        <v>10.262</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>5.027</v>
+        <v>10.63</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>3.35</v>
+        <v>3.343</v>
       </c>
     </row>
     <row r="82">
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>1.983</v>
+        <v>5.901</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>1.895</v>
+        <v>5.528</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.483</v>
+        <v>7.094</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.298</v>
@@ -6811,13 +6811,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>570464.22</v>
+        <v>987410.8</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>693408.97</v>
+        <v>1074044.82</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>433381.85</v>
+        <v>918529.12</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>285537.23</v>
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-40204.63</v>
+        <v>-455964.95</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-171284.28</v>
+        <v>-550752.0699999999</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-2309.17</v>
+        <v>-486492.07</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>140621.75</v>
+        <v>141575.13</v>
       </c>
     </row>
     <row r="85">
@@ -6852,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>-0</v>
@@ -6902,16 +6902,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>431072.68</v>
+        <v>432037.05</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>426158.98</v>
+        <v>427112.36</v>
       </c>
     </row>
     <row r="90">
@@ -6940,13 +6940,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>1951815.71</v>
+        <v>4036548.62</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2228321.44</v>
+        <v>4131500.68</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>1403041.46</v>
+        <v>3828777.8</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>650269.66</v>
@@ -6959,16 +6959,16 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>1421556.12</v>
+        <v>3505102.77</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>1706196.75</v>
+        <v>3608207.93</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>971968.78</v>
+        <v>3396740.75</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>224110.68</v>
+        <v>223157.3</v>
       </c>
     </row>
     <row r="93">
@@ -6978,16 +6978,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>431072.68</v>
+        <v>432037.05</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>426158.98</v>
+        <v>427112.36</v>
       </c>
     </row>
     <row r="94">
@@ -7130,16 +7130,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>431072.68</v>
+        <v>432037.05</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>426158.98</v>
+        <v>427112.36</v>
       </c>
     </row>
     <row r="102">
@@ -7233,16 +7233,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8759.92</v>
+        <v>8776.99</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>110556.04</v>
+        <v>110757.38</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>64317.16</v>
+        <v>64621.99</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>186918.49</v>
+        <v>187059.26</v>
       </c>
     </row>
     <row r="6">
@@ -7252,16 +7252,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>131.37</v>
+        <v>416.93</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>656.83</v>
+        <v>2084.63</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>2758.69</v>
+        <v>8755.459999999999</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>19310.81</v>
+        <v>61288.22</v>
       </c>
     </row>
     <row r="7">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>159892.52</v>
+        <v>2244625.43</v>
       </c>
     </row>
     <row r="9">
@@ -7315,16 +7315,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>625.02</v>
+        <v>623.9</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>11369.14</v>
+        <v>11348.58</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-39783.45</v>
+        <v>-39711.51</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>68825.75</v>
+        <v>67780.25999999999</v>
       </c>
     </row>
     <row r="12">
@@ -7397,16 +7397,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>8134.9</v>
+        <v>8153.1</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>99186.91</v>
+        <v>99408.8</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>104100.61</v>
+        <v>104333.49</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>118092.74</v>
+        <v>119279</v>
       </c>
     </row>
     <row r="18">
@@ -7416,16 +7416,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>197.2</v>
+        <v>482.62</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>986</v>
+        <v>2413.09</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>4141.22</v>
+        <v>10134.98</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>28988.53</v>
+        <v>70944.88</v>
       </c>
     </row>
     <row r="19">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>146238.94</v>
+        <v>2230971.85</v>
       </c>
     </row>
     <row r="21">
@@ -7517,13 +7517,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -7536,16 +7536,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>8759.92</v>
+        <v>8776.99</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>110556.04</v>
+        <v>110757.38</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>64317.16</v>
+        <v>64621.99</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>186918.49</v>
+        <v>187059.26</v>
       </c>
     </row>
     <row r="7">
@@ -7593,16 +7593,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="10">
@@ -7615,13 +7615,13 @@
         <v>0.8</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>11.08</v>
+        <v>11.1</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>6.16</v>
+        <v>6.19</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>20.28</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="11">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-0.85</v>
+        <v>-0.86</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>-5.24</v>
@@ -7684,13 +7684,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>566788.55</v>
+        <v>565763.62</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>617941.14</v>
+        <v>616823.71</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -7703,16 +7703,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>625.02</v>
+        <v>623.9</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>11369.14</v>
+        <v>11348.58</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-39783.45</v>
+        <v>-39711.51</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>68825.75</v>
+        <v>67780.25999999999</v>
       </c>
     </row>
     <row r="17">
@@ -7760,16 +7760,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
     </row>
     <row r="20">
@@ -7788,7 +7788,7 @@
         <v>-6.44</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>13.51</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="21">
@@ -7851,13 +7851,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>431072.68</v>
+        <v>432037.05</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>426158.98</v>
+        <v>427112.36</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -7870,16 +7870,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>8134.9</v>
+        <v>8153.1</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>99186.91</v>
+        <v>99408.8</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>104100.61</v>
+        <v>104333.49</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>118092.74</v>
+        <v>119279</v>
       </c>
     </row>
     <row r="27">
@@ -7927,16 +7927,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
     </row>
     <row r="30">
@@ -7955,7 +7955,7 @@
         <v>24.43</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>28.65</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="31">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>110556.04</v>
+        <v>110757.38</v>
       </c>
     </row>
     <row r="5">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-426959.08</v>
+        <v>-85955.64999999999</v>
       </c>
     </row>
     <row r="6">
@@ -8043,8 +8043,8 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>312920.61</v>
+      <c r="B6" s="19" t="n">
+        <v>-28284.16</v>
       </c>
     </row>
     <row r="7">
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -9091,7 +9091,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -9201,7 +9201,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -9281,7 +9281,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -9291,7 +9291,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -9391,7 +9391,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -9421,7 +9421,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -9441,7 +9441,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -9551,7 +9551,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -9561,7 +9561,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
   </sheetData>
@@ -9696,31 +9696,31 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2047699.95</v>
+        <v>4132432.86</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>984486.4399999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3032186.39</v>
+        <v>5116919.3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1063213.51</v>
+        <v>3147946.42</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>2.736</v>
+        <v>4.616</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.959</v>
+        <v>2.84</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>273.56</v>
+        <v>461.58</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>136.78</v>
+        <v>230.79</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>18</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>578157.6899999999</v>
+        <v>577112.2</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>95884.24000000001</v>
@@ -9748,16 +9748,16 @@
         <v>11903.2</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>0.021</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>31.11</v>
+        <v>31.17</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>15.56</v>
+        <v>15.58</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>1</v>
@@ -9770,31 +9770,31 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>530259.59</v>
+        <v>531445.85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1951815.71</v>
+        <v>4036548.62</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>900505.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2852321.11</v>
+        <v>4937054.02</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1051310.31</v>
+        <v>3136043.22</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>5.379</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.983</v>
+        <v>5.901</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>537.91</v>
+        <v>928.99</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>268.96</v>
+        <v>464.49</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>17</v>
@@ -9835,7 +9835,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.0611  ·  effective N pairs=16.4  ·  max pair=8.64% of gross</t>
+          <t>HHI=0.1345  ·  effective N pairs=7.4  ·  max pair=28.1% of gross</t>
         </is>
       </c>
     </row>
@@ -9874,20 +9874,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>361162.9</v>
+        <v>2316369.9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>361162.9</v>
+        <v>2316369.9</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>32.58</v>
+        <v>208.95</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>11.91</v>
+        <v>45.27</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -9896,20 +9896,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>296278.02</v>
+        <v>361162.9</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>296278.02</v>
+        <v>361162.9</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>26.73</v>
+        <v>32.58</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>9.77</v>
+        <v>7.06</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -9918,20 +9918,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>276230.52</v>
+        <v>296278.02</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>276230.52</v>
+        <v>296278.02</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>24.92</v>
+        <v>26.73</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>9.109999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -9940,20 +9940,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>231636.99</v>
+        <v>276230.52</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>231636.99</v>
+        <v>276230.52</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>20.9</v>
+        <v>24.92</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>7.64</v>
+        <v>5.4</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>2</v>
@@ -9972,10 +9972,10 @@
         <v>230736</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>20.82</v>
+        <v>20.81</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>7.61</v>
+        <v>4.51</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>2</v>
@@ -9997,7 +9997,7 @@
         <v>15.59</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>5.7</v>
+        <v>3.38</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -10019,7 +10019,7 @@
         <v>15.3</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>5.59</v>
+        <v>3.31</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>2</v>
@@ -10041,7 +10041,7 @@
         <v>12.42</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>4.54</v>
+        <v>2.69</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>2</v>
@@ -10063,7 +10063,7 @@
         <v>11.95</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>4.37</v>
+        <v>2.59</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>2</v>
@@ -10082,10 +10082,10 @@
         <v>-100597.64</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>3.32</v>
+        <v>1.97</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>2</v>
@@ -10132,16 +10132,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1052772.55</v>
+        <v>3137505.46</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>126135.72</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>926636.83</v>
+        <v>3011369.74</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>30.56</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="21">
@@ -10160,7 +10160,7 @@
         <v>445816.86</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>14.7</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -10179,7 +10179,7 @@
         <v>-426045.65</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-14.05</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="23">
@@ -10198,7 +10198,7 @@
         <v>402044.18</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>13.26</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="24">
@@ -10217,7 +10217,7 @@
         <v>-184524.16</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-6.09</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="25">
@@ -10236,7 +10236,7 @@
         <v>-100714.55</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-3.32</v>
+        <v>-1.97</v>
       </c>
     </row>
   </sheetData>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.833</v>
+        <v>5.762</v>
       </c>
     </row>
     <row r="4">
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.757</v>
+        <v>6.687</v>
       </c>
     </row>
     <row r="5">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>94.84999999999999</v>
+        <v>282.89</v>
       </c>
     </row>
     <row r="6">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>30.56</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="11">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>14.7</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>-14.05</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="13">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>13.26</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="14">
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-6.09</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="15">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>-3.32</v>
+        <v>-1.97</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-03  ·  Generated 2026-06-24T18:50:02  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-03  ·  Generated 2026-06-25T01:16:23  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-03  ·  Generated 2026-06-25T01:16:23  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-03  ·  Generated 2026-06-25T01:35:11  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>

--- a/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260603_180742.xlsx
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-03  ·  Generated 2026-06-25T01:35:11  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-03  ·  Generated 2026-06-25T01:48:35  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4.616</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="6">
@@ -758,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.84</v>
+      <c r="B6" s="6" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5.762</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>111661.88</v>
+        <v>38394.23</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10.07</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97.2</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="11">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>4.616</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (208.95% NAV)</t>
+          <t>BWA (32.58% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>58.85</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="18">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>111661.88</v>
+        <v>38394.23</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>157887.86</v>
+        <v>54288.74</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1077554.62</v>
+        <v>370510.33</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>97.2</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>81798.92</v>
+        <v>26685.64</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>97861.73</v>
+        <v>28974.03</v>
       </c>
     </row>
     <row r="10">
@@ -1024,157 +1024,157 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>53536.23</v>
+        <v>5927.26</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>47.94</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>32953.32</v>
+        <v>4816.52</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>29.51</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5801.84</v>
+        <v>3890.43</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5.2</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>4958.97</v>
+        <v>3182.2</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>4.44</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2016.79</v>
+        <v>2784.76</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1.81</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1909.68</v>
+        <v>2127.92</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>1.71</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1566.85</v>
+        <v>2056.89</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1.4</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>1539.34</v>
+        <v>2008.59</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1.38</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>1535.35</v>
+        <v>1774.32</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.38</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>1399.55</v>
+        <v>1703.79</v>
       </c>
       <c r="C21" s="17" t="n">
-        <v>1.25</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>1365.52</v>
+        <v>1687.93</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>1087.79</v>
+        <v>1647.3</v>
       </c>
       <c r="C23" s="17" t="n">
-        <v>0.97</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="24">
@@ -1184,36 +1184,36 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>646.25</v>
+        <v>1455.49</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0.58</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>502.56</v>
+        <v>1348.72</v>
       </c>
       <c r="C25" s="17" t="n">
-        <v>0.45</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>475.25</v>
+        <v>808.65</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0.43</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1422,7 @@
         <v>670</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1015148</v>
+        <v>10151477</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>420</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1015148</v>
+        <v>10151477</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-319375.57</v>
+        <v>-101599.35</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-28.81</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="5">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-638751.15</v>
+        <v>-203198.69</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>-57.62</v>
+        <v>-18.33</v>
       </c>
     </row>
     <row r="6">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-319375.57</v>
+        <v>-101599.35</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-28.81</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="7">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-301136.97</v>
+        <v>-92663.67999999999</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>-27.16</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9.289999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="D6" s="32" t="n">
         <v>3</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>5.9</v>
+        <v>1.98</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>208.95</v>
+        <v>32.58</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>32.58</v>
+        <v>26.73</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1915,80 +1915,80 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="D10" s="32" t="n">
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="D10" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="F10" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>58.85</v>
-      </c>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="34" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="D11" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>max_pair</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D12" s="34" t="n">
+      <c r="C12" s="30" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="D12" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E12" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>5.76</v>
+        <v>1.83</v>
       </c>
       <c r="D13" s="32" t="n">
         <v>0.3</v>
@@ -2019,28 +2019,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>var_95_1d</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="D14" s="32" t="n">
+      <c r="C14" s="34" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="D14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="32" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -2469,10 +2469,10 @@
         <v>670</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>2125.11</v>
+        <v>212.51</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>1423823.7</v>
+        <v>142382.37</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
@@ -2645,10 +2645,10 @@
         <v>420</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>2125.11</v>
+        <v>212.51</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>892546.2</v>
+        <v>89254.62</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1289420.98</v>
+        <v>7979.65</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1438059.55</v>
+        <v>156618.22</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>815508.88</v>
+        <v>12217.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>971868.5</v>
+        <v>168576.92</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
@@ -4676,71 +4676,71 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>LRCX/BSX</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>47.94</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>KLAC/LOW</t>
+          <t>LRCX/RMD</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>29.51</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/BSX</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>5.2</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>LRCX/RMD</t>
+          <t>STLD/HII</t>
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>4.44</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/HII</t>
+          <t>STLD/ISRG</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1.81</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>STLD/ISRG</t>
+          <t>KLAC/LOW</t>
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1.71</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>CSCO/CAG</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>1.4</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="20">
@@ -4750,47 +4750,47 @@
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1.38</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>BWA/CME</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.38</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>ODFL/MKTX</t>
+          <t>FFIV/VLTO</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>1.25</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>CSCO/CAG</t>
+          <t>ODFL/MKTX</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>FFIV/VLTO</t>
+          <t>BWA/CME</t>
         </is>
       </c>
       <c r="B24" s="17" t="n">
-        <v>0.97</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="25">
@@ -4800,27 +4800,27 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0.58</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>BWA/VLTO</t>
+          <t>CSCO/REGN</t>
         </is>
       </c>
       <c r="B26" s="17" t="n">
-        <v>0.45</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>CSCO/REGN</t>
+          <t>BWA/VLTO</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>0.43</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>
@@ -5316,7 +5316,7 @@
         <v>4.53</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>4.616</v>
+        <v>2.735</v>
       </c>
     </row>
     <row r="10">
@@ -5384,7 +5384,7 @@
         <v>1.55</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>9.289999999999999</v>
+        <v>5.367</v>
       </c>
     </row>
   </sheetData>
@@ -5497,13 +5497,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4132432.86</v>
+        <v>2047699.95</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4228553.42</v>
+        <v>2325374.18</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4049891.36</v>
+        <v>1624155.02</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>752511.91</v>
@@ -5516,13 +5516,13 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>5136609.03</v>
+        <v>3051876.12</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5578806.73</v>
+        <v>3675627.49</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>5057549.96</v>
+        <v>2631813.62</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>1925990.6</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>3043564.54</v>
+        <v>958831.63</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>3155247.92</v>
+        <v>1252068.68</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>3071848.7</v>
+        <v>646112.36</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -5573,13 +5573,13 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4028050.98</v>
+        <v>1943318.07</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4479025.67</v>
+        <v>2575846.43</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4059749.29</v>
+        <v>1634012.95</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>882054.54</v>
@@ -5611,13 +5611,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4.616</v>
+        <v>2.735</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>5.049</v>
+        <v>3.318</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5.049</v>
+        <v>2.618</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>1.566</v>
@@ -5630,13 +5630,13 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>2.84</v>
+        <v>0.959</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>2.641</v>
+        <v>0.911</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>3.069</v>
+        <v>0.638</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>-0.124</v>
@@ -5649,13 +5649,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>1023383.86</v>
+        <v>606437.28</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1110466.23</v>
+        <v>729830.39</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1007558.39</v>
+        <v>522411.12</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>326913.29</v>
@@ -5668,13 +5668,13 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>85174.19</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>-10685.17</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>-9757.719999999999</v>
+        <v>502120.77</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>369950.67</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>475389.55</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>717022.77</v>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>-0</v>
@@ -5778,13 +5778,13 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>4132432.86</v>
+        <v>2047699.95</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4228553.42</v>
+        <v>2325374.18</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4049891.36</v>
+        <v>1624155.02</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>752511.91</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>3023874.81</v>
+        <v>939141.9</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>3128772.36</v>
+        <v>1225593.12</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>3052090.69</v>
+        <v>626354.35</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -6659,13 +6659,13 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>4036548.62</v>
+        <v>1951815.71</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>4131500.68</v>
+        <v>2228321.44</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>3828777.8</v>
+        <v>1403041.46</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>650269.66</v>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="B76" s="13" t="n">
-        <v>4955064.13</v>
+        <v>2870331.22</v>
       </c>
       <c r="C76" s="13" t="n">
-        <v>5394998.56</v>
+        <v>3491819.32</v>
       </c>
       <c r="D76" s="13" t="n">
-        <v>4607922.95</v>
+        <v>2182186.61</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>1443234.48</v>
@@ -6716,13 +6716,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>3523112.88</v>
+        <v>1438379.97</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>3632982.4</v>
+        <v>1729803.16</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>3412018.11</v>
+        <v>986281.77</v>
       </c>
       <c r="E78" s="13" t="n">
         <v>238705.63</v>
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>4423618.28</v>
+        <v>2338885.37</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4871705.81</v>
+        <v>2968526.57</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>4175885.9</v>
+        <v>1750149.56</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>1016122.12</v>
@@ -6773,13 +6773,13 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>9.289999999999999</v>
+        <v>5.367</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>10.262</v>
+        <v>6.625</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>10.63</v>
+        <v>5.016</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>3.343</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>5.901</v>
+        <v>1.978</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>5.528</v>
+        <v>1.891</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>7.094</v>
+        <v>1.479</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.298</v>
@@ -6811,13 +6811,13 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>987410.8</v>
+        <v>570464.22</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1074044.82</v>
+        <v>693408.97</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>918529.12</v>
+        <v>433381.85</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>285537.23</v>
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="B84" s="18" t="n">
-        <v>-455964.95</v>
+        <v>-39018.37</v>
       </c>
       <c r="C84" s="18" t="n">
-        <v>-550752.0699999999</v>
+        <v>-170116.22</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-486492.07</v>
+        <v>-1344.8</v>
       </c>
       <c r="E84" s="13" t="n">
         <v>141575.13</v>
@@ -6855,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -6940,13 +6940,13 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>4036548.62</v>
+        <v>1951815.71</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4131500.68</v>
+        <v>2228321.44</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>3828777.8</v>
+        <v>1403041.46</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>650269.66</v>
@@ -6959,13 +6959,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>3505102.77</v>
+        <v>1420369.86</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>3608207.93</v>
+        <v>1705028.69</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>3396740.75</v>
+        <v>971004.41</v>
       </c>
       <c r="E92" s="13" t="n">
         <v>223157.3</v>
@@ -7111,13 +7111,13 @@
         </is>
       </c>
       <c r="B100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="15" t="n">
         <v>-0</v>
-      </c>
-      <c r="C100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="E100" s="15" t="n">
         <v>0</v>
@@ -7252,16 +7252,16 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>416.93</v>
+        <v>131.35</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>2084.63</v>
+        <v>656.73</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>8755.459999999999</v>
+        <v>2758.28</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>61288.22</v>
+        <v>19307.98</v>
       </c>
     </row>
     <row r="7">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2244625.43</v>
+        <v>159892.52</v>
       </c>
     </row>
     <row r="9">
@@ -7416,16 +7416,16 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>482.62</v>
+        <v>197.04</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>2413.09</v>
+        <v>985.1900000000001</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>10134.98</v>
+        <v>4137.81</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>70944.88</v>
+        <v>28964.64</v>
       </c>
     </row>
     <row r="19">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>2230971.85</v>
+        <v>146238.94</v>
       </c>
     </row>
     <row r="21">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-85955.64999999999</v>
+        <v>-426959.08</v>
       </c>
     </row>
     <row r="6">
@@ -8043,8 +8043,8 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>-28284.16</v>
+      <c r="B6" s="4" t="n">
+        <v>312719.27</v>
       </c>
     </row>
     <row r="7">
@@ -9699,28 +9699,28 @@
         <v>1108558.05</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4132432.86</v>
+        <v>2047699.95</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>984486.4399999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5116919.3</v>
+        <v>3032186.39</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3147946.42</v>
+        <v>1063213.51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>4.616</v>
+        <v>2.735</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.84</v>
+        <v>0.959</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>461.58</v>
+        <v>273.53</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>230.79</v>
+        <v>136.76</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>18</v>
@@ -9773,28 +9773,28 @@
         <v>531445.85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4036548.62</v>
+        <v>1951815.71</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>900505.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4937054.02</v>
+        <v>2852321.11</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3136043.22</v>
+        <v>1051310.31</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>9.289999999999999</v>
+        <v>5.367</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5.901</v>
+        <v>1.978</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>928.99</v>
+        <v>536.71</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>464.49</v>
+        <v>268.35</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>17</v>
@@ -9835,7 +9835,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1345  ·  effective N pairs=7.4  ·  max pair=28.1% of gross</t>
+          <t>HHI=0.0611  ·  effective N pairs=16.4  ·  max pair=8.64% of gross</t>
         </is>
       </c>
     </row>
@@ -9874,20 +9874,20 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>2316369.9</v>
+        <v>361162.9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2316369.9</v>
+        <v>361162.9</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>208.95</v>
+        <v>32.58</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>45.27</v>
+        <v>11.91</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -9896,20 +9896,20 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>361162.9</v>
+        <v>296278.02</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>361162.9</v>
+        <v>296278.02</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>32.58</v>
+        <v>26.73</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>7.06</v>
+        <v>9.77</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -9918,20 +9918,20 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>296278.02</v>
+        <v>276230.52</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>296278.02</v>
+        <v>276230.52</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>26.73</v>
+        <v>24.92</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>5.79</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -9940,20 +9940,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>276230.52</v>
+        <v>231636.99</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>276230.52</v>
+        <v>231636.99</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>24.92</v>
+        <v>20.9</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>5.4</v>
+        <v>7.64</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>2</v>
@@ -9975,7 +9975,7 @@
         <v>20.81</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>4.51</v>
+        <v>7.61</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>2</v>
@@ -9997,7 +9997,7 @@
         <v>15.59</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>3.38</v>
+        <v>5.7</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -10019,7 +10019,7 @@
         <v>15.3</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>3.31</v>
+        <v>5.59</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>2</v>
@@ -10041,7 +10041,7 @@
         <v>12.42</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>2.69</v>
+        <v>4.54</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>2</v>
@@ -10063,7 +10063,7 @@
         <v>11.95</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>2.59</v>
+        <v>4.37</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>2</v>
@@ -10085,7 +10085,7 @@
         <v>9.07</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>1.97</v>
+        <v>3.32</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>2</v>
@@ -10132,16 +10132,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>3137505.46</v>
+        <v>1052772.55</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>126135.72</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3011369.74</v>
+        <v>926636.83</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>58.85</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="21">
@@ -10160,7 +10160,7 @@
         <v>445816.86</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>8.710000000000001</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="22">
@@ -10179,7 +10179,7 @@
         <v>-426045.65</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-8.33</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="23">
@@ -10198,7 +10198,7 @@
         <v>402044.18</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>7.86</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="24">
@@ -10217,7 +10217,7 @@
         <v>-184524.16</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-3.61</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="25">
@@ -10236,7 +10236,7 @@
         <v>-100714.55</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-1.97</v>
+        <v>-3.32</v>
       </c>
     </row>
   </sheetData>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.762</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="4">
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>6.687</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="5">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>282.89</v>
+        <v>94.84</v>
       </c>
     </row>
     <row r="6">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>58.85</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="11">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>8.710000000000001</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="12">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>-8.33</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="13">
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>7.86</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="14">
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-3.61</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="15">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>-1.97</v>
+        <v>-3.32</v>
       </c>
     </row>
   </sheetData>
